--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Эксперт_оценки MoSCoW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нечеткий MoSCoW_итог" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица_взаимосвязей_FR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нечеткий MoSCoW_итог" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,10 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -158,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -187,8 +192,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -580,12 +599,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -636,7 +655,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -653,17 +672,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -680,12 +699,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -707,7 +726,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -724,7 +743,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -741,12 +760,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -763,7 +782,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -773,7 +792,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -790,12 +809,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -807,17 +826,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -834,12 +853,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -859,660 +878,1397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>альфа</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="n">
+          <t>Матрица взаимосвязанности функциональных требований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Нечеткий MoSCoW — итоговая приоритизация (один эксперт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>1) Параметры дефаззификации</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>a (редукция типа CLTR)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>alpha (уровень альфа-среза)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>0.8</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2) Итоговые нечеткие приоритеты и результаты дефаззификации</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Итоговый приоритет функционального требования в виде нечеткого числа</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>Дефаззификация при заданном уровне альфа-среза</t>
-        </is>
-      </c>
-      <c r="O3" s="13" t="inlineStr">
-        <is>
-          <t>Расчет центроида</t>
-        </is>
-      </c>
-      <c r="Q3" s="13" t="inlineStr">
-        <is>
-          <t>Центроид_итог</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Верхняя функция принадлежности</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Нижняя функция принадлежности</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>Верхний альфа-срез</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr">
-        <is>
-          <t>Нижний альфа-срез</t>
-        </is>
-      </c>
-      <c r="O4" s="13" t="inlineStr">
-        <is>
-          <t>Верхняя ФП</t>
-        </is>
-      </c>
-      <c r="P4" s="13" t="inlineStr">
-        <is>
-          <t>Нижняя ФП</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Итоговый приоритет функционального требования в виде ИНМТ2</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Редуцированный приоритет FR в виде ИНМТ1</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>Дефаззификация (альфа-срез)</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>Центроид</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>UMF_x1</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>UMF_x2</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>UMF_x3</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>UMF_x4</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>LMF_x1</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>LMF_x2</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>LMF_x3</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>LMF_x4</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>T1_x1</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>T1_x2</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>T1_x3</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>T1_x4</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>alpha_start</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <t>alpha_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="H5" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="J5" t="n">
-        <v>19.03</v>
-      </c>
-      <c r="K5" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="L5" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="M5" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="N5" t="n">
-        <v>16.45</v>
-      </c>
-      <c r="O5" t="n">
-        <v>14.07</v>
-      </c>
-      <c r="P5" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>14.08</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="C11" s="14" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="P11" s="14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Q11" s="14" t="n">
+        <v>23.16</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="F6" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="I6" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18.36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M6" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="O6" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12.62</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="C12" s="14" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="O12" s="14" t="n">
+        <v>17.74</v>
+      </c>
+      <c r="P12" s="14" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="Q12" s="14" t="n">
+        <v>20.73</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="F7" t="n">
-        <v>20.66</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="I7" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="J7" t="n">
-        <v>18.63</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="C13" s="14" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="O13" s="14" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="P13" s="14" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="Q13" s="14" t="n">
         <v>15.86</v>
       </c>
-      <c r="M7" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="N7" t="n">
-        <v>15.45</v>
-      </c>
-      <c r="O7" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>12.57</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="E8" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="F8" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="I8" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="N8" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="C14" s="14" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="N14" s="14" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="O14" s="14" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="P14" s="14" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="Q14" s="14" t="n">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="O15" s="14" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="Q15" s="14" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="O16" s="14" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="Q16" s="14" t="n">
+        <v>12.96</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="O17" s="14" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="Q17" s="14" t="n">
+        <v>10.72</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="O18" s="14" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="Q18" s="14" t="n">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="N19" s="14" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="O19" s="14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P19" s="14" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="Q19" s="14" t="n">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="F9" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="M9" t="n">
-        <v>7.79</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="P9" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="C20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="O20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Q20" s="14" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>3) Скорректированный рейтинг FR с учетом взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Исходный центроид</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Скорректированный центроид</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>23.16</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>23.16</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>15.86</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>15.86</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>15.86</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>10.72</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="E10" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="F10" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="I10" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="L10" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="M10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N10" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FR7</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="E11" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="F11" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="I11" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="J11" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="L11" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="M11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="O11" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="C32" s="14" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>10.72</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="E12" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="F12" t="n">
-        <v>19.96</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="H12" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="J12" t="n">
-        <v>17.49</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="L12" t="n">
-        <v>14.16</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="N12" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="O12" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>10.38</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="F13" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="H13" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="I13" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="J13" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="N13" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="O13" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="P13" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>8.51</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E14" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="F14" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9.07</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="N14" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="P14" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.88</v>
+      <c r="C33" s="14" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>5.58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
@@ -163,15 +163,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,6 +183,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -198,7 +198,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,6 +206,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -556,7 +559,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.85546875" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -565,7 +568,7 @@
     <row r="1"/>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -587,22 +590,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -643,220 +646,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -881,17 +884,17 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1345,27 +1348,27 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Нечеткий MoSCoW — итоговая приоритизация (один эксперт)</t>
+          <t>Нечеткий MoSCoW - итоговая приоритизация (один эксперт)</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1398,7 @@
           <t>a (редукция типа CLTR)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="17" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1405,7 +1408,7 @@
           <t>alpha (уровень альфа-среза)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1525,54 +1528,54 @@
       <c r="A11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="17" t="n">
         <v>12.83</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="17" t="n">
         <v>14.13</v>
       </c>
-      <c r="L11" s="14" t="n">
+      <c r="L11" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="N11" s="14" t="n">
+      <c r="N11" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="O11" s="14" t="n">
+      <c r="O11" s="17" t="n">
         <v>20.83</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="17" t="n">
         <v>23.16</v>
       </c>
     </row>
@@ -1580,54 +1583,54 @@
       <c r="A12" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="17" t="n">
         <v>11.04</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="17" t="n">
         <v>19.12</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="17" t="n">
         <v>23.54</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="17" t="n">
         <v>24.57</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="17" t="n">
         <v>12.97</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="17" t="n">
         <v>19.12</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="17" t="n">
         <v>23.54</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="17" t="n">
         <v>24.31</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="17" t="n">
         <v>12.2</v>
       </c>
-      <c r="L12" s="14" t="n">
+      <c r="L12" s="17" t="n">
         <v>19.12</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="17" t="n">
         <v>23.54</v>
       </c>
-      <c r="N12" s="14" t="n">
+      <c r="N12" s="17" t="n">
         <v>24.41</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O12" s="17" t="n">
         <v>17.74</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="17" t="n">
         <v>23.71</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="Q12" s="17" t="n">
         <v>20.73</v>
       </c>
     </row>
@@ -1635,54 +1638,54 @@
       <c r="A13" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>7.44</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="17" t="n">
         <v>12.38</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="17" t="n">
         <v>19.63</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="17" t="n">
         <v>22.71</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="17" t="n">
         <v>8.94</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="17" t="n">
         <v>12.38</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="17" t="n">
         <v>19.63</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="17" t="n">
         <v>21.93</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="17" t="n">
         <v>8.34</v>
       </c>
-      <c r="L13" s="14" t="n">
+      <c r="L13" s="17" t="n">
         <v>12.38</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="17" t="n">
         <v>19.63</v>
       </c>
-      <c r="N13" s="14" t="n">
+      <c r="N13" s="17" t="n">
         <v>22.24</v>
       </c>
-      <c r="O13" s="14" t="n">
+      <c r="O13" s="17" t="n">
         <v>11.57</v>
       </c>
-      <c r="P13" s="14" t="n">
+      <c r="P13" s="17" t="n">
         <v>20.15</v>
       </c>
-      <c r="Q13" s="14" t="n">
+      <c r="Q13" s="17" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -1690,54 +1693,54 @@
       <c r="A14" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>4.96</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="17" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="17" t="n">
         <v>16.82</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="17" t="n">
         <v>19.82</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="17" t="n">
         <v>6.19</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="17" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="17" t="n">
         <v>16.82</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="17" t="n">
         <v>19.04</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="17" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L14" s="17" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="17" t="n">
         <v>16.82</v>
       </c>
-      <c r="N14" s="14" t="n">
+      <c r="N14" s="17" t="n">
         <v>19.35</v>
       </c>
-      <c r="O14" s="14" t="n">
+      <c r="O14" s="17" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="P14" s="14" t="n">
+      <c r="P14" s="17" t="n">
         <v>17.33</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="Q14" s="17" t="n">
         <v>13.19</v>
       </c>
     </row>
@@ -1745,54 +1748,54 @@
       <c r="A15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="17" t="n">
         <v>6.76</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="17" t="n">
         <v>11.62</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="17" t="n">
         <v>15.04</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="17" t="n">
         <v>17.94</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="17" t="n">
         <v>7.98</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="17" t="n">
         <v>11.62</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="17" t="n">
         <v>15.04</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="17" t="n">
         <v>17.08</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="17" t="n">
         <v>7.49</v>
       </c>
-      <c r="L15" s="14" t="n">
+      <c r="L15" s="17" t="n">
         <v>11.62</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="M15" s="17" t="n">
         <v>15.04</v>
       </c>
-      <c r="N15" s="14" t="n">
+      <c r="N15" s="17" t="n">
         <v>17.42</v>
       </c>
-      <c r="O15" s="14" t="n">
+      <c r="O15" s="17" t="n">
         <v>10.79</v>
       </c>
-      <c r="P15" s="14" t="n">
+      <c r="P15" s="17" t="n">
         <v>15.52</v>
       </c>
-      <c r="Q15" s="14" t="n">
+      <c r="Q15" s="17" t="n">
         <v>13.15</v>
       </c>
     </row>
@@ -1800,54 +1803,54 @@
       <c r="A16" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="17" t="n">
         <v>4.28</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="17" t="n">
         <v>15.98</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="17" t="n">
         <v>17.86</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="17" t="n">
         <v>5.46</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="17" t="n">
         <v>15.98</v>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="17" t="n">
         <v>17.34</v>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="17" t="n">
         <v>4.99</v>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="L16" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="17" t="n">
         <v>15.98</v>
       </c>
-      <c r="N16" s="14" t="n">
+      <c r="N16" s="17" t="n">
         <v>17.55</v>
       </c>
-      <c r="O16" s="14" t="n">
+      <c r="O16" s="17" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="P16" s="14" t="n">
+      <c r="P16" s="17" t="n">
         <v>16.29</v>
       </c>
-      <c r="Q16" s="14" t="n">
+      <c r="Q16" s="17" t="n">
         <v>12.96</v>
       </c>
     </row>
@@ -1855,54 +1858,54 @@
       <c r="A17" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="17" t="n">
         <v>4.96</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="17" t="n">
         <v>8.25</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="17" t="n">
         <v>13.09</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="17" t="n">
         <v>17.01</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="17" t="n">
         <v>5.96</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H17" s="17" t="n">
         <v>8.25</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="I17" s="17" t="n">
         <v>13.09</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="17" t="n">
         <v>15.89</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="17" t="n">
         <v>5.56</v>
       </c>
-      <c r="L17" s="14" t="n">
+      <c r="L17" s="17" t="n">
         <v>8.25</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="17" t="n">
         <v>13.09</v>
       </c>
-      <c r="N17" s="14" t="n">
+      <c r="N17" s="17" t="n">
         <v>16.34</v>
       </c>
-      <c r="O17" s="14" t="n">
+      <c r="O17" s="17" t="n">
         <v>7.71</v>
       </c>
-      <c r="P17" s="14" t="n">
+      <c r="P17" s="17" t="n">
         <v>13.74</v>
       </c>
-      <c r="Q17" s="14" t="n">
+      <c r="Q17" s="17" t="n">
         <v>10.72</v>
       </c>
     </row>
@@ -1910,54 +1913,54 @@
       <c r="A18" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="14" t="n">
+      <c r="C18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="17" t="n">
         <v>4.95</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="17" t="n">
         <v>11.22</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="17" t="n">
         <v>14.04</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="17" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="17" t="n">
         <v>4.95</v>
       </c>
-      <c r="I18" s="14" t="n">
+      <c r="I18" s="17" t="n">
         <v>11.22</v>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="J18" s="17" t="n">
         <v>13.26</v>
       </c>
-      <c r="K18" s="14" t="n">
+      <c r="K18" s="17" t="n">
         <v>0.41</v>
       </c>
-      <c r="L18" s="14" t="n">
+      <c r="L18" s="17" t="n">
         <v>4.95</v>
       </c>
-      <c r="M18" s="14" t="n">
+      <c r="M18" s="17" t="n">
         <v>11.22</v>
       </c>
-      <c r="N18" s="14" t="n">
+      <c r="N18" s="17" t="n">
         <v>13.57</v>
       </c>
-      <c r="O18" s="14" t="n">
+      <c r="O18" s="17" t="n">
         <v>4.04</v>
       </c>
-      <c r="P18" s="14" t="n">
+      <c r="P18" s="17" t="n">
         <v>11.69</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="17" t="n">
         <v>7.87</v>
       </c>
     </row>
@@ -1965,54 +1968,54 @@
       <c r="A19" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>2.48</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>4.12</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="17" t="n">
         <v>6.54</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="17" t="n">
         <v>11.31</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G19" s="17" t="n">
         <v>2.98</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="17" t="n">
         <v>4.12</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="17" t="n">
         <v>6.54</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="17" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="17" t="n">
         <v>2.78</v>
       </c>
-      <c r="L19" s="14" t="n">
+      <c r="L19" s="17" t="n">
         <v>4.12</v>
       </c>
-      <c r="M19" s="14" t="n">
+      <c r="M19" s="17" t="n">
         <v>6.54</v>
       </c>
-      <c r="N19" s="14" t="n">
+      <c r="N19" s="17" t="n">
         <v>10.44</v>
       </c>
-      <c r="O19" s="14" t="n">
+      <c r="O19" s="17" t="n">
         <v>3.85</v>
       </c>
-      <c r="P19" s="14" t="n">
+      <c r="P19" s="17" t="n">
         <v>7.32</v>
       </c>
-      <c r="Q19" s="14" t="n">
+      <c r="Q19" s="17" t="n">
         <v>5.58</v>
       </c>
     </row>
@@ -2020,54 +2023,54 @@
       <c r="A20" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14" t="n">
+      <c r="C20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="17" t="n">
         <v>5.61</v>
       </c>
-      <c r="G20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="14" t="n">
+      <c r="G20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17" t="n">
         <v>3.81</v>
       </c>
-      <c r="K20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="14" t="n">
+      <c r="K20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="17" t="n">
         <v>4.53</v>
       </c>
-      <c r="O20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="14" t="n">
+      <c r="O20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="17" t="n">
         <v>0.91</v>
       </c>
-      <c r="Q20" s="14" t="n">
+      <c r="Q20" s="17" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -2105,15 +2108,15 @@
       <c r="A24" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>23.16</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="17" t="n">
         <v>23.16</v>
       </c>
     </row>
@@ -2121,15 +2124,15 @@
       <c r="A25" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>20.73</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>23.16</v>
       </c>
     </row>
@@ -2137,15 +2140,15 @@
       <c r="A26" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>15.86</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -2153,15 +2156,15 @@
       <c r="A27" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>12.96</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -2169,15 +2172,15 @@
       <c r="A28" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>0.46</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -2185,15 +2188,15 @@
       <c r="A29" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="17" t="n">
         <v>13.19</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="17" t="n">
         <v>13.19</v>
       </c>
     </row>
@@ -2201,15 +2204,15 @@
       <c r="A30" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="17" t="n">
         <v>13.15</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="17" t="n">
         <v>13.15</v>
       </c>
     </row>
@@ -2217,15 +2220,15 @@
       <c r="A31" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="17" t="n">
         <v>10.72</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="17" t="n">
         <v>10.72</v>
       </c>
     </row>
@@ -2233,15 +2236,15 @@
       <c r="A32" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="17" t="n">
         <v>7.87</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D32" s="17" t="n">
         <v>10.72</v>
       </c>
     </row>
@@ -2249,15 +2252,15 @@
       <c r="A33" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="17" t="n">
         <v>5.58</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="17" t="n">
         <v>5.58</v>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
@@ -1376,7 +1376,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>1) Параметры дефаззификации</t>
+          <t>1) Гиперпараметры модели</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_один эксперт.xlsx
@@ -1376,7 +1376,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>1) Гиперпараметры модели</t>
+          <t>1) Параметры модели</t>
         </is>
       </c>
     </row>
